--- a/26년 찬조리스트.xlsx
+++ b/26년 찬조리스트.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/710b81175c7ce6a3/문서/카카오톡 받은 파일/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yj202\Downloads\claude_p1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{ABEEC421-EB38-4E0E-8B4B-10959BAF2837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D522F6AE-32AD-47EE-90B5-E2F64BE06465}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92281D63-02A1-4CDD-B1D8-A6D7C3C00282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{600FC321-F743-482B-B6E1-EF52D54E4837}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>이현영 원우님</t>
   </si>
@@ -248,6 +248,18 @@
   </si>
   <si>
     <t>굿베이스 석류담은 홍삼 1세트</t>
+  </si>
+  <si>
+    <t>김준표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김승인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이재웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -349,7 +361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -382,6 +394,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C62F0D-F64A-4AA8-B336-3F1BAB85A0B6}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.75" style="10" customWidth="1"/>
@@ -888,319 +906,355 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="5">
+        <v>460000</v>
+      </c>
       <c r="D18"/>
     </row>
-    <row r="19" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19"/>
-      <c r="B19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
+      <c r="B19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="3">
+        <v>100000</v>
+      </c>
       <c r="D19"/>
     </row>
-    <row r="20" spans="1:4" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20"/>
-      <c r="B20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>16</v>
+      <c r="B20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5">
+        <v>460000</v>
       </c>
       <c r="D20"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21"/>
-      <c r="B21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
       <c r="D21"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22"/>
-      <c r="B22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
       <c r="D22"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23"/>
-      <c r="B23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1"/>
       <c r="D23"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A24"/>
-      <c r="B24" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>24</v>
+      <c r="B24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="D24"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25"/>
       <c r="B25" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D25"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26"/>
       <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27"/>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28"/>
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D28"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29"/>
       <c r="B29" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30"/>
       <c r="B30" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31"/>
       <c r="B31" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32"/>
       <c r="B32" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D32"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33"/>
       <c r="B33" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D33"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34"/>
       <c r="B34" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35"/>
       <c r="B35" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36"/>
       <c r="B36" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37"/>
       <c r="B37" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38"/>
       <c r="B38" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39"/>
       <c r="B39" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D39"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40"/>
       <c r="B40" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D40"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41"/>
       <c r="B41" s="4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D41"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42"/>
       <c r="B42" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D42"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43"/>
       <c r="B43" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D43"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44"/>
       <c r="B44" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45"/>
       <c r="B45" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D45"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46"/>
       <c r="B46" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D46"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47"/>
       <c r="B47" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48"/>
-      <c r="B48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>68</v>
+      <c r="B48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D48"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49"/>
+      <c r="B49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="D49"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50"/>
+      <c r="B50" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51"/>
+      <c r="B51" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52"/>
+      <c r="B52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
